--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488189_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488189_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2302</v>
+        <v>6.7794</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5769</v>
+        <v>3.2739</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6533</v>
+        <v>3.5055</v>
       </c>
       <c r="G2" t="n">
         <v>5.3258</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7812</v>
+        <v>-0.2319</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6056</v>
+        <v>0.0914</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1756</v>
+        <v>-0.3234</v>
       </c>
       <c r="V2" t="n">
         <v>0.9444</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6163</v>
+        <v>6.2952</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7884</v>
+        <v>3.3443</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8278</v>
+        <v>2.9509</v>
       </c>
       <c r="G3" t="n">
         <v>4.8022</v>
@@ -688,13 +688,13 @@
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7037</v>
+        <v>-1.0247</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.2139</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9339</v>
+        <v>-0.8108</v>
       </c>
       <c r="V3" t="n">
         <v>2.5177</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7034</v>
+        <v>3.1207</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1906</v>
+        <v>-0.8751</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5128</v>
+        <v>3.9957</v>
       </c>
       <c r="G4" t="n">
         <v>2.8435</v>
@@ -766,13 +766,13 @@
         <v>1.297</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1013</v>
+        <v>0.5185</v>
       </c>
       <c r="T4" t="n">
-        <v>1.353</v>
+        <v>0.2873</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7483</v>
+        <v>0.2313</v>
       </c>
       <c r="V4" t="n">
         <v>0.3144</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. KANTE</t>
+          <t>Á. LLAMAS JIMENEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7008</v>
+        <v>1.2662</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7738</v>
+        <v>1.2662</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.073</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7862</v>
+        <v>1.2662</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1948</v>
+        <v>0.6441</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4086</v>
+        <v>0.6221</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1472</v>
+        <v>1.2662</v>
       </c>
       <c r="K5" t="n">
-        <v>1.095</v>
+        <v>0.6441</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0522</v>
+        <v>0.6221</v>
       </c>
       <c r="M5" t="n">
-        <v>0.639</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0997</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4607</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4878</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.553</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Á. LLAMAS JIMENEZ</t>
+          <t>O. KANTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2662</v>
+        <v>1.1142</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2662</v>
+        <v>1.3595</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.2454</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2662</v>
+        <v>1.7862</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6441</v>
+        <v>2.1948</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6221</v>
+        <v>-0.4086</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2662</v>
+        <v>1.1472</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6441</v>
+        <v>1.095</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6221</v>
+        <v>0.0522</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.639</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.0997</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.4607</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.9013</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.1388</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.2375</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Y. VAQUERO HERNANDEZ</t>
+          <t>M. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8681</v>
+        <v>-0.5444</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5401</v>
+        <v>-3.7719</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6719000000000001</v>
+        <v>3.2275</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4242</v>
+        <v>1.8005</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5548</v>
+        <v>2.1721</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1306</v>
+        <v>-0.3716</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6099</v>
+        <v>0.0613</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6099</v>
+        <v>-0.0738</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.1351</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1857</v>
+        <v>1.7392</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0552</v>
+        <v>2.2459</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1306</v>
+        <v>-0.5067</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1117</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8529</v>
+        <v>-3.7057</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7411</v>
+        <v>1.6676</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6677999999999999</v>
+        <v>-0.3078</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9227</v>
+        <v>-0.1274</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2549</v>
+        <v>-0.1804</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.0011</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. BRAVO ORTEGA</t>
+          <t>C. CORRALES GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1483</v>
+        <v>-0.9369</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.5236</v>
+        <v>-0.2644</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3753</v>
+        <v>-0.6725</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8005</v>
+        <v>-1.1729</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1721</v>
+        <v>-0.408</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3716</v>
+        <v>-0.765</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0613</v>
+        <v>-0.5899</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0738</v>
+        <v>0.0215</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1351</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7392</v>
+        <v>-0.583</v>
       </c>
       <c r="N8" t="n">
-        <v>2.2459</v>
+        <v>-0.4294</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5067</v>
+        <v>-0.1536</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9118000000000001</v>
+        <v>0.236</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8792</v>
+        <v>0.3255</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0326</v>
+        <v>-0.0895</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. CORRALES GARCIA</t>
+          <t>Y. VAQUERO HERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5059</v>
+        <v>-1.4737</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8088</v>
+        <v>-2.2688</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6972</v>
+        <v>0.7951</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1729</v>
+        <v>-0.4242</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.408</v>
+        <v>-0.5548</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.765</v>
+        <v>0.1306</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5899</v>
+        <v>-0.6099</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0215</v>
+        <v>-0.6099</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.583</v>
+        <v>0.1857</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4294</v>
+        <v>0.0552</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1536</v>
+        <v>0.1306</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.333</v>
+        <v>0.0622</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2189</v>
+        <v>0.194</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1142</v>
+        <v>-0.1318</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. KONE</t>
+          <t>J. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7025</v>
+        <v>-1.9254</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.035</v>
+        <v>-2.8618</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3325</v>
+        <v>0.9364</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5683</v>
+        <v>-2.0999</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.109</v>
+        <v>-0.524</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4593</v>
+        <v>-1.5759</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2552</v>
+        <v>-2.4084</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9494</v>
+        <v>-1.8385</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3057</v>
+        <v>-0.5699</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3131</v>
+        <v>0.3085</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1596</v>
+        <v>1.3144</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1536</v>
+        <v>-1.006</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.297</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R10" t="n">
         <v>0.5558999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.2307</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.1586</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0898</v>
+        <v>0.0721</v>
       </c>
       <c r="V10" t="n">
         <v>0.3144</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BRAVO ORTEGA</t>
+          <t>S. KONE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2302</v>
+        <v>-3.0833</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8958</v>
+        <v>-3.3173</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6656</v>
+        <v>0.234</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0999</v>
+        <v>-2.5683</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.524</v>
+        <v>-1.109</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5759</v>
+        <v>-1.4593</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4084</v>
+        <v>-2.2552</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8385</v>
+        <v>-0.9494</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5699</v>
+        <v>-1.3057</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3085</v>
+        <v>-0.3131</v>
       </c>
       <c r="N11" t="n">
-        <v>1.3144</v>
+        <v>-0.1596</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.006</v>
+        <v>-0.1536</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3706</v>
+        <v>-1.297</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R11" t="n">
         <v>0.5558999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0742</v>
+        <v>0.4676</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8754</v>
+        <v>0.4763</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1987</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>0.3144</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3055</v>
+        <v>-3.9553</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0574</v>
+        <v>-3.0026</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2481</v>
+        <v>-0.9527</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7879</v>
@@ -1390,13 +1390,13 @@
         <v>0.9264</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0555</v>
+        <v>0.2947</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0584</v>
+        <v>-0.0037</v>
       </c>
       <c r="U12" t="n">
-        <v>0.003</v>
+        <v>0.2984</v>
       </c>
       <c r="V12" t="n">
         <v>-3.4621</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.0227</v>
+        <v>-5.8289</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.722</v>
+        <v>-5.7745</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3007</v>
+        <v>-0.0545</v>
       </c>
       <c r="G13" t="n">
         <v>-4.0977</v>
@@ -1468,13 +1468,13 @@
         <v>0.9264</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3517</v>
+        <v>-0.1579</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5508999999999999</v>
+        <v>0.3967</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.5546</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5733</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2663000000000029</v>
+        <v>0.8278000000000025</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.9868</v>
+        <v>-12.8925</v>
       </c>
       <c r="F14" t="n">
-        <v>13.7202</v>
+        <v>13.72</v>
       </c>
       <c r="G14" t="n">
-        <v>6.673499999999999</v>
+        <v>6.673500000000001</v>
       </c>
       <c r="H14" t="n">
         <v>13.2021</v>
@@ -1519,10 +1519,10 @@
         <v>-6.528700000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.215199999999999</v>
+        <v>-5.215199999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6824</v>
+        <v>-0.6824000000000002</v>
       </c>
       <c r="L14" t="n">
         <v>-4.5329</v>
@@ -1537,7 +1537,7 @@
         <v>-1.9956</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.632299999999999</v>
+        <v>-4.6323</v>
       </c>
       <c r="Q14" t="n">
         <v>-15.7493</v>
@@ -1546,10 +1546,10 @@
         <v>11.1172</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1059000000000003</v>
+        <v>0.9887</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6292</v>
+        <v>2.723600000000001</v>
       </c>
       <c r="U14" t="n">
         <v>-1.7349</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. TRAORE</t>
+          <t>R. RUBIO SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3361</v>
+        <v>2.6399</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1329</v>
+        <v>0.8534</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2032</v>
+        <v>1.7866</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4411</v>
+        <v>0.7518</v>
       </c>
       <c r="H15" t="n">
-        <v>1.106</v>
+        <v>-0.8903</v>
       </c>
       <c r="I15" t="n">
-        <v>0.335</v>
+        <v>1.642</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9469</v>
+        <v>-1.187</v>
       </c>
       <c r="K15" t="n">
-        <v>0.781</v>
+        <v>-1.1776</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1659</v>
+        <v>-0.0094</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4942</v>
+        <v>1.9388</v>
       </c>
       <c r="N15" t="n">
-        <v>0.325</v>
+        <v>0.2873</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1692</v>
+        <v>1.6514</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3706</v>
+        <v>1.297</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0382</v>
+        <v>-1.1117</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6676</v>
+        <v>2.4087</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9514</v>
+        <v>-0.6675</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5953</v>
+        <v>0.3199</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3561</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3142</v>
+        <v>1.2586</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6289</v>
+        <v>2.8321</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3147</v>
+        <v>-1.5735</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. RUBIO SANCHEZ</t>
+          <t>I. TRAORE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4178</v>
+        <v>2.4744</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9513</v>
+        <v>0.4681</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4665</v>
+        <v>2.0062</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7518</v>
+        <v>1.4411</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8903</v>
+        <v>1.106</v>
       </c>
       <c r="I16" t="n">
-        <v>1.642</v>
+        <v>0.335</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.187</v>
+        <v>0.9469</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.1776</v>
+        <v>0.781</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0094</v>
+        <v>0.1659</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9388</v>
+        <v>0.4942</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2873</v>
+        <v>0.325</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6514</v>
+        <v>0.1692</v>
       </c>
       <c r="P16" t="n">
-        <v>1.297</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1117</v>
+        <v>-2.0382</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4087</v>
+        <v>1.6676</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8895999999999999</v>
+        <v>1.0896</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4179</v>
+        <v>0.9305</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3075</v>
+        <v>0.1591</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2586</v>
+        <v>0.3142</v>
       </c>
       <c r="W16" t="n">
-        <v>2.8321</v>
+        <v>0.6289</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5735</v>
+        <v>-0.3147</v>
       </c>
     </row>
     <row r="17">
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1075</v>
+        <v>0.9698</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0501</v>
+        <v>0.0272</v>
       </c>
       <c r="F17" t="n">
         <v>0.9426</v>
@@ -1780,10 +1780,10 @@
         <v>1.297</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8593</v>
+        <v>0.2179</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0184</v>
+        <v>0.0588</v>
       </c>
       <c r="U17" t="n">
         <v>0.1591</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.43</v>
+        <v>-0.2341</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0684</v>
+        <v>0.2643</v>
       </c>
       <c r="F18" t="n">
         <v>-0.4984</v>
@@ -1858,10 +1858,10 @@
         <v>0.7411</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.48</v>
+        <v>-0.2841</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1131</v>
+        <v>0.0827</v>
       </c>
       <c r="U18" t="n">
         <v>-0.3669</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ROSA CABRERA</t>
+          <t>A. CHAPARRO CARRASCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4992</v>
+        <v>-0.6707</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1083</v>
+        <v>-1.3017</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3909</v>
+        <v>0.631</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6996</v>
+        <v>-0.3169</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0022</v>
+        <v>-1.6748</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3026</v>
+        <v>1.3579</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9179</v>
+        <v>0.0335</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8978</v>
+        <v>-1.2628</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0201</v>
+        <v>1.2963</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2183</v>
+        <v>-0.3504</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1044</v>
+        <v>-0.412</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3227</v>
+        <v>0.0616</v>
       </c>
       <c r="P19" t="n">
-        <v>1.297</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R19" t="n">
-        <v>1.297</v>
+        <v>0.9264</v>
       </c>
       <c r="S19" t="n">
-        <v>0.287</v>
+        <v>0.0202</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8096</v>
+        <v>-0.2235</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5226</v>
+        <v>0.2437</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3836</v>
+        <v>-0.1888</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3836</v>
+        <v>-0.1888</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8525</v>
+        <v>-1.1698</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2313</v>
+        <v>-2.7209</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3788</v>
+        <v>1.5511</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2138</v>
@@ -2014,13 +2014,13 @@
         <v>0.9264</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2878</v>
+        <v>-0.0295</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.2689</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4708</v>
+        <v>-0.2985</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CHAPARRO CARRASCO</t>
+          <t>J. ROSA CABRERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4547</v>
+        <v>-1.3641</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9872</v>
+        <v>-0.9897</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5325</v>
+        <v>-0.3745</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3169</v>
+        <v>-0.6996</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6748</v>
+        <v>-1.0022</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3579</v>
+        <v>0.3026</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0335</v>
+        <v>-0.9179</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2628</v>
+        <v>-0.8978</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2963</v>
+        <v>-0.0201</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3504</v>
+        <v>0.2183</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.412</v>
+        <v>-0.1044</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0616</v>
+        <v>0.3227</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1853</v>
+        <v>1.297</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9264</v>
+        <v>1.297</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7638</v>
+        <v>-0.5779</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.909</v>
+        <v>-0.0718</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1452</v>
+        <v>-0.5061</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1888</v>
+        <v>-1.3836</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1888</v>
+        <v>-1.3836</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. NDOUR</t>
+          <t>S. VALIENTE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6028</v>
+        <v>-1.5603</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.5488</v>
+        <v>-4.6248</v>
       </c>
       <c r="F22" t="n">
-        <v>3.946</v>
+        <v>3.0645</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.401</v>
+        <v>-1.6074</v>
       </c>
       <c r="H22" t="n">
-        <v>-6.5164</v>
+        <v>-3.9392</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1154</v>
+        <v>2.3318</v>
       </c>
       <c r="J22" t="n">
-        <v>-7.4814</v>
+        <v>-3.2854</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.383</v>
+        <v>-4.6646</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.0984</v>
+        <v>1.3792</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0803</v>
+        <v>1.678</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1334</v>
+        <v>0.7255</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2137</v>
+        <v>0.9526</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.0382</v>
       </c>
       <c r="R22" t="n">
-        <v>3.1499</v>
+        <v>2.2234</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3587</v>
+        <v>-0.138</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1953</v>
+        <v>0.3843</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1634</v>
+        <v>-0.5223</v>
       </c>
       <c r="V22" t="n">
-        <v>2.3278</v>
+        <v>-0.0002</v>
       </c>
       <c r="W22" t="n">
-        <v>3.7755</v>
+        <v>0.3144</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4476</v>
+        <v>-0.3147</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. VALIENTE RODRIGUEZ</t>
+          <t>B. NDOUR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4176</v>
+        <v>-2.1696</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4083</v>
+        <v>-5.4509</v>
       </c>
       <c r="F23" t="n">
-        <v>2.9906</v>
+        <v>3.2812</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6074</v>
+        <v>-6.401</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.9392</v>
+        <v>-6.5164</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3318</v>
+        <v>0.1154</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.2854</v>
+        <v>-7.4814</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.6646</v>
+        <v>-6.383</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3792</v>
+        <v>-1.0984</v>
       </c>
       <c r="M23" t="n">
-        <v>1.678</v>
+        <v>1.0803</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7255</v>
+        <v>-0.1334</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9526</v>
+        <v>1.2137</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.0382</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2234</v>
+        <v>3.1499</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9953</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3991</v>
+        <v>0.2932</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5962</v>
+        <v>0.4986</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.0002</v>
+        <v>2.3278</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3144</v>
+        <v>3.7755</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3147</v>
+        <v>-1.4476</v>
       </c>
     </row>
     <row r="24">
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6104000000000003</v>
+        <v>-1.084500000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-13.1814</v>
+        <v>-13.475</v>
       </c>
       <c r="F24" t="n">
-        <v>12.5709</v>
+        <v>12.3903</v>
       </c>
       <c r="G24" t="n">
-        <v>-7.229800000000001</v>
+        <v>-7.2298</v>
       </c>
       <c r="H24" t="n">
         <v>-12.9337</v>
@@ -2326,13 +2326,13 @@
         <v>14.6375</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8968999999999999</v>
+        <v>0.4224999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3371</v>
+        <v>2.043</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.4402</v>
+        <v>-1.6207</v>
       </c>
       <c r="V24" t="n">
         <v>2.2021</v>
